--- a/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="57">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationElectrogardiogramDuration_CS</t>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationElectrocardiogramDuration_CS</t>
   </si>
   <si>
     <t>Version</t>
@@ -36,13 +36,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>JP_ObservationElectrogardiogramDuration_CS</t>
+    <t>JP_ObservationElectrocardiogramDuration_CS</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>JP Core Observation ElectroCardioGram Duration CodeSystem</t>
+    <t>JP Core Observation Electrocardiogram Duration CodeSystem</t>
   </si>
   <si>
     <t>Status</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>7</t>
   </si>
   <si>
     <t>Level</t>
@@ -142,6 +142,30 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>JECGDU0010</t>
+  </si>
+  <si>
+    <t>30s</t>
+  </si>
+  <si>
+    <t>JECGDU0020</t>
+  </si>
+  <si>
+    <t>1m</t>
+  </si>
+  <si>
+    <t>JECGDU0030</t>
+  </si>
+  <si>
+    <t>3m</t>
+  </si>
+  <si>
+    <t>JECGDU0040</t>
+  </si>
+  <si>
+    <t>5m</t>
   </si>
   <si>
     <t>JECGDU0100</t>
@@ -471,7 +495,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -524,6 +548,54 @@
       </c>
       <c r="D4" s="2"/>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>Case Sensitive</t>
